--- a/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>MTB</t>
   </si>
@@ -656,271 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2412000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2301000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2350000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2388000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2271000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2176000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2245000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2212000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2152000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2060000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2075000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2185000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2452000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2285000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2072200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1781500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2393400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>928300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>958500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>992900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>970400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1017000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1038900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1001200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2152700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1120400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1185900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1229500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1237900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1226300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1220300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1167400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2211100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1082200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1074100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1057200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1030400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1006000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>982900</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>969500</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1041,53 +1047,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2412000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2301000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2350000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2388000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2271000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2176000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2245000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2212000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2152000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2060000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2075000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2185000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2452000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2285000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1495,8 +1514,8 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1573,67 +1592,70 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E15" s="3">
         <v>97000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>122000</v>
       </c>
       <c r="F15" s="3">
         <v>122000</v>
       </c>
       <c r="G15" s="3">
+        <v>122000</v>
+      </c>
+      <c r="H15" s="3">
         <v>124000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>130000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>129000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>122000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>127000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>130000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>129000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>130000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>125000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>113000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-17600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-18400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-19600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-1300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-2000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>-2700</v>
       </c>
       <c r="W15" s="3">
         <v>-2700</v>
@@ -1642,61 +1664,64 @@
         <v>-2700</v>
       </c>
       <c r="Y15" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="Z15" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-4300</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>-5100</v>
       </c>
       <c r="AE15" s="3">
         <v>-5100</v>
       </c>
       <c r="AF15" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="AG15" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-5400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-13000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-6600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-7000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-7800</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-8100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-8400</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-9100</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1324000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1406000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1377000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1340000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1305000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1379000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1326000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1266000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1247000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1321000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1206000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1234000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1250000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1312000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>334800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>217800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>389500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>34100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>24700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>28000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>35600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>49600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>58100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>218700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>143600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>231100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>244600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>251400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>198200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>199300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>154300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>304800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>149600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>133700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>130100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>144200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>146800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>169100</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>158200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1088000</v>
+      </c>
+      <c r="E18" s="3">
         <v>895000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>973000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1048000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>966000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>797000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>919000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>946000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>905000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>739000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>869000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>951000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1202000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>973000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1737400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1563700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2003900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>894200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>933800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>967200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>942400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>981400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>989300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>943100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1934000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>976800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>954800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>984900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>986500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1028100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1021000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1013100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1906300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>932600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>940400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>927100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>886200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>859200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>813800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>811300</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,252 +2056,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E20" s="3">
         <v>32000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>23000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>31000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>36000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>37000</v>
       </c>
       <c r="J20" s="3">
         <v>37000</v>
       </c>
       <c r="K20" s="3">
+        <v>37000</v>
+      </c>
+      <c r="L20" s="3">
         <v>50000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>75000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>243000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>44000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>43000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>47000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-726700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-716200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1250900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-418900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-333800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-310200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-336800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-388900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-368800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-456300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1271900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-627000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-302600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-349900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-360900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-393600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-321600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-316700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-793900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-474700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-311700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-346600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-289800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-341000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-303600</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-261000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1156000</v>
+      </c>
+      <c r="E21" s="3">
         <v>960000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1093000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1147000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1059000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>891000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1011000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1031000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>982000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>794000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>755000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1037000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1284000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1039000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1090500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>950700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>907600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>533300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>656900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>715600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>664700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>652400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>679900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>546400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>778700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>408400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>710700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>693900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>681600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>690500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>729400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>728600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1179600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>491800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>660700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>618100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>632000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>554100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>546300</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>586500</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1063000</v>
+      </c>
+      <c r="E23" s="3">
         <v>863000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>971000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1025000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>935000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>761000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>882000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>909000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>855000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>664000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>626000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>907000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1159000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>926000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1010600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>847500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>753000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>475300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>599900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>657000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>605600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>592500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>620500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>486900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>662100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>349700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>652200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>635100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>625500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>634500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>699400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>696400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1112500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>457900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>628700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>580500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>596400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>518300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>510100</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>550300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E24" s="3">
         <v>199000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>212000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>233000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>219000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>177000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>201000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>188000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>133000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>144000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>217000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>292000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>224000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>245300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>173300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>113100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>142000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>161600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>147600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>145300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>149400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>114700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>152200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>80900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>159100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>155000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>152300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>151700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>153200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>170300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>266700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>105300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>220900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>224600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>215300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>169300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>179500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>200300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>818000</v>
+      </c>
+      <c r="E26" s="3">
         <v>664000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>759000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>792000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>716000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>584000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>681000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>721000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>655000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>531000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>482000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>690000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>867000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>702000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>765400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>646600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>579700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>362200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>458000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>495500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>458100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>447200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>471100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>372100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>509900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>268800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>493100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>480100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>473300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>482700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>546200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>526100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>845800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>352600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>407800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>355900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>381100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>348900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>330600</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>350000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>781000</v>
+      </c>
+      <c r="E27" s="3">
         <v>620000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>718000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>754000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>679000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>547000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>644000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>674000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>626000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>505000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>456000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>664000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>841000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>676000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>739100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>620500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>531900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>339700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>434200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>476000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>438800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>428100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>451900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>353400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>473800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>250700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>473400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>461400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>452600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>462100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>525300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>505400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>805300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>332700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>387900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>335800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>360700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>328600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>307800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3268,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3226,12 +3286,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-85400</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-32000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-23000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-31000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-36000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-37000</v>
       </c>
       <c r="J32" s="3">
         <v>-37000</v>
       </c>
       <c r="K32" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="L32" s="3">
         <v>-50000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-75000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-243000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-44000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-43000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-47000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>726700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>716200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1250900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>418900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>333800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>310200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>336800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>388900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>368800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>456300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1271900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>627000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>302600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>349900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>360900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>393600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>321600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>316700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>793900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>474700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>311700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>346600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>289800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>341000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>303600</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>261000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>818000</v>
+      </c>
+      <c r="E33" s="3">
         <v>664000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>759000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>792000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>716000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>584000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>681000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>721000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>655000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>531000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>482000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>690000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>867000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>702000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>739100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>620500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>531900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>339700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>434200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>476000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>438800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>428100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>451900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>353400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>473800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>250700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>473400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>461400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>452600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>462100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>525300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>505400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>805300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>332700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>302500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>335800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>360700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>328600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>307800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>818000</v>
+      </c>
+      <c r="E35" s="3">
         <v>664000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>759000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>792000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>716000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>584000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>681000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>721000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>655000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>531000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>482000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>690000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>867000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>702000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>739100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>620500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>531900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>339700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>434200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>476000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>438800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>428100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>451900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>353400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>473800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>250700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>473400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>461400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>452600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>462100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>525300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>505400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>805300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>332700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>302500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>335800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>360700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>328600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>307800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,297 +4276,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17438000</v>
+      </c>
+      <c r="E41" s="3">
         <v>16348000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>18769000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1950000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2128000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2109000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20782000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2216000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1778000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1695000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1731000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1768900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1848400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1817700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1517200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2255800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1688300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1411500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1337600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1479700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1410500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1259000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1552700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1489200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1354800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1298200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1432800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1818900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1271600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1267300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1605400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1311600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1367600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1291700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1420900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1368300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1344500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1287000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1320500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1332200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E42" s="3">
         <v>309000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>342000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>17099000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>19635000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>20970000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>356000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>24783000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>25164000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>32539000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>28477000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>30649600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>27596900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>22812600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>26011500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>26355800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>34545200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>36693900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>42805700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>39540100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>35042600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>32563700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>25206500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>23058400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>23893000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>11799100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>8588100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>14306400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>10267200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>8580300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>9113500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>7226000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>7424000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>6896500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>5704900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>7003000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>5822200</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>7704000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>6064700</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>11748700</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E43" s="3">
         <v>73000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>75000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>68000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>71000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>68000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>72000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>69000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>67000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>63000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>68000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>61000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>63000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>68000</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4557,53 +4649,56 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E44" s="3">
         <v>27000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>35000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>37000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>30000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>34000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>35000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>37000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>33000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>38000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>39000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>37100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>42700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>44600</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -4679,53 +4774,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9204000</v>
+      </c>
+      <c r="E45" s="3">
         <v>9393000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8310000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8523000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>210000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7868000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6877000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6875000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7355000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9198000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>808000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>756000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>717000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>715000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27497000</v>
+      </c>
+      <c r="E46" s="3">
         <v>26150000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>28456000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>27677000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22074000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>31049000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>28643000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>34938000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>34774000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>44261000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>31123000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>33703600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>30806100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>25930900</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,53 +5024,56 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>40331000</v>
+      </c>
+      <c r="E47" s="3">
         <v>40556000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>38616000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>38611000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>37234000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>36663000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>35607000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>33801000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>31335000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>28496000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>26897000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>27336100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>27916500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>28443200</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5045,252 +5149,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1726000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1716000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1813000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1621000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1646000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1661000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1909000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1694000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1719000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1707000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1739000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1681100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1673000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1664000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1653600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1620300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1600200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1134700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1144800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1117900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1116700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1148900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1161600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1146700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1155300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1154600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1140900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1074200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1066500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1044800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>647400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>634400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>637800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>628700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>646500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>656700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>673600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>672800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>675300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>660400</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9189000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8520000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8948000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8539000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8549000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8558000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9053000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8572000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8584000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8597000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9262000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8627400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8642300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8682300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8699500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8728300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8746700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4595900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4597100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4599100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4601800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4604500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4607300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4610400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4614300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>4618200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>4622100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>4626500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>4631500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>4637100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>4640200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>4645500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4651700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>4658100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4664700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>4671700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>4679500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>4687600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>4690800</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>4699900</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,8 +5649,11 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5548,16 +5667,16 @@
         <v>16000</v>
       </c>
       <c r="G52" s="3">
+        <v>16000</v>
+      </c>
+      <c r="H52" s="3">
         <v>8162000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>22000</v>
       </c>
       <c r="K52" s="3">
         <v>22000</v>
@@ -5566,20 +5685,20 @@
         <v>22000</v>
       </c>
       <c r="M52" s="3">
+        <v>22000</v>
+      </c>
+      <c r="N52" s="3">
         <v>7304000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7904700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7826500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7746400</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5655,8 +5774,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>219261000</v>
+      </c>
+      <c r="E54" s="3">
         <v>214736000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>213510000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>211277000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>211584000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>210321000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>208105000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>211785000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>208855000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>215137000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>208264000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>209124300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>207671700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>202956400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>200729800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>197955500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>204032900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>149863600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>155107200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>151901200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>150622700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>150481100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>142601100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>138626700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>139537000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>124577800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>119872800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>125500900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>121554900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>120025200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>120097400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>116827600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>118426100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>118622800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>118593500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>120401800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>120896600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>123223300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>123449200</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>126841000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,180 +6116,184 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>168885000</v>
+      </c>
+      <c r="E57" s="3">
         <v>163741000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>166909000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>163426000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>164453000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>165409000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>161095000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>164554000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>159910000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>167196000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>163274000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>164127800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>162058400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>159075200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4377500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4476500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3743300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2174900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2127900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2067200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2042900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2000700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2166400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1719500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2095300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2033400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1762800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1562200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1388700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1346500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1446700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1489800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1663800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1506900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1454800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1678100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1607600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1551700</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1634600</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1633100</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5117000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8276000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2756000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2539000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2625000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2205000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1882000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3284000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5805000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5867000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6259000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8220500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9203400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8059200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4299100</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -6231,8 +6364,11 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6275,8 +6411,8 @@
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
@@ -6308,24 +6444,24 @@
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>487600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>424900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>422400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>420000</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>5</v>
       </c>
@@ -6335,8 +6471,8 @@
       <c r="AJ59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK59" s="3">
-        <v>0</v>
+      <c r="AK59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL59" s="3">
         <v>0</v>
@@ -6353,53 +6489,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>176761000</v>
+      </c>
+      <c r="E60" s="3">
         <v>174548000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>171812000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>168769000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>169930000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>170079000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>165009000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>170815000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>168639000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>176466000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>169533000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>172750000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>171651000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>167317400</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,175 +6614,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13568000</v>
+      </c>
+      <c r="E61" s="3">
         <v>11175000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>11410000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12928000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12380000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10496000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13282000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11583000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11319000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11450000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8918000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7123400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7416600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7462900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3220400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3459300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3017400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3443600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3485400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3500400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3499400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3498500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4382200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5458900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6321300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6321400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6986200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7002500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>7655500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8476000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8444900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9140300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>8382300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>8591100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>8141400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>8577600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>7649600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>8087600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>9493800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>10211200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>936000</v>
+      </c>
+      <c r="E62" s="3">
         <v>989000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1057000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>798000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>697000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>700000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>730000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>458000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>422000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N62" s="3">
         <v>2802000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3003400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2754100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2754000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6719,8 +6864,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>191315000</v>
+      </c>
+      <c r="E66" s="3">
         <v>186764000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>184333000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>182549000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>183059000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>181330000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>179078000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>182909000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>180431000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>187968000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>181307000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>182927800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>181870800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>177579200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>175411900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>172699000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>178238400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>131987500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>137203800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>134372400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>133902400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>134034600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>126413800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>122525700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>123591900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>108762000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>104156100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>109721100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>105863100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>104437700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>104637200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>101391600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>102848200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>102913100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>102342700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>104083800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>104613000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>107010100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>106962600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>110500100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7504,10 +7671,10 @@
         <v>2434000</v>
       </c>
       <c r="E70" s="3">
+        <v>2434000</v>
+      </c>
+      <c r="F70" s="3">
         <v>2834000</v>
-      </c>
-      <c r="F70" s="3">
-        <v>2394000</v>
       </c>
       <c r="G70" s="3">
         <v>2394000</v>
@@ -7522,16 +7689,16 @@
         <v>2394000</v>
       </c>
       <c r="K70" s="3">
+        <v>2394000</v>
+      </c>
+      <c r="L70" s="3">
         <v>2744000</v>
-      </c>
-      <c r="L70" s="3">
-        <v>2011000</v>
       </c>
       <c r="M70" s="3">
         <v>2011000</v>
       </c>
       <c r="N70" s="3">
-        <v>2010600</v>
+        <v>2011000</v>
       </c>
       <c r="O70" s="3">
         <v>2010600</v>
@@ -7549,7 +7716,7 @@
         <v>2010600</v>
       </c>
       <c r="T70" s="3">
-        <v>1750000</v>
+        <v>2010600</v>
       </c>
       <c r="U70" s="3">
         <v>1750000</v>
@@ -7558,7 +7725,7 @@
         <v>1750000</v>
       </c>
       <c r="W70" s="3">
-        <v>1250000</v>
+        <v>1750000</v>
       </c>
       <c r="X70" s="3">
         <v>1250000</v>
@@ -7582,7 +7749,7 @@
         <v>1250000</v>
       </c>
       <c r="AE70" s="3">
-        <v>1231500</v>
+        <v>1250000</v>
       </c>
       <c r="AF70" s="3">
         <v>1231500</v>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>1231500</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>1231500</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>22038000</v>
+      </c>
+      <c r="E72" s="3">
         <v>21476000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20882000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20392000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>19870000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>19405000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19079000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>18659000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18211000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>17812000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17524000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17284400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16836800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16212100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15754000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15219800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14808600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14830700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14646400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14365900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14030200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>13731900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>13444400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13132400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>12919300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>12837400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12820900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12490200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>12162300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>11842400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>11516700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>11128300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>10763600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>10404500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>10164800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9909400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>9685500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>9437500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>9222500</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>9022000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25512000</v>
+      </c>
+      <c r="E76" s="3">
         <v>25538000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26343000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26334000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>26131000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>26597000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>26633000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26482000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25680000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25158000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24946000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>24185900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23790300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23366600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23307400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>23245900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>23783900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16126000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16153400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15778800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15470300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15196500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>14937300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14851000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>14695100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14565800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14466600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14529800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14460300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14356000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14228700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14204600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14346400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>14478200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>15019300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>15086600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>15052000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>14981600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>15255100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>15109500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>818000</v>
+      </c>
+      <c r="E81" s="3">
         <v>664000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>759000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>792000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>716000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>584000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>681000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>721000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>655000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>531000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>482000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>690000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>867000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>702000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>739100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>620500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>531900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>339700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>434200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>476000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>438800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>428100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>451900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>353400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>473800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>250700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>473400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>461400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>452600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>462100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>525300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>505400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>805300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>332700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>302500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>335800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>360700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>328600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>307800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E83" s="3">
         <v>83000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>81000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>76000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>79000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>80000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>77000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>78000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>73000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>76000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>62300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>84800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>78200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>56700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>79900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>103200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>154600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>58000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>57000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>58500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>59100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>59900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>59400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>59500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>116600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>58700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>58500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>58800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>56100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>56000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>30000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>32200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>67100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>33900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>32000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>37500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>35600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>35800</v>
-      </c>
-      <c r="AO83" s="3">
-        <v>36200</v>
       </c>
       <c r="AP83" s="3">
         <v>36200</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>36200</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1268000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1012000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>523000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1001000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>844000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>635000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1676000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-28000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1354000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>608000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>800000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1420000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1257000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>428000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>953600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1137000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2483100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1295800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>696900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>486300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>537000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>994700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>664100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>131100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-394400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1130700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>746700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>66900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>413300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>550200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1018400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>521200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>484200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>716100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>442600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>337500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1285800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>111300</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>422100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-96000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-56000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-36000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-26000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-25000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-85000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-30000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-66000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-35000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-88000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-67000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-46000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-87600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-39100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-59800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-27900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-62000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-42700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-31000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-46900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-31700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-93700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-51500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-58500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-36900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-51900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-30700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-38400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-37100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-9500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-28300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-21500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-42400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-28700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3826000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4324000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3832000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-853000</v>
-      </c>
       <c r="H94" s="3">
+        <v>-2212000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-349000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6903000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1386000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>5625000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7082000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>683000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1907000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4903000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1747000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3665100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>6219300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>14038600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>4195600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3453400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1195800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-50600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-8931700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4043500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>967300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-18944200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3852400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>4726700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3418800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-852100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>271300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2946800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>873700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>663000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-248500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>1215600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>514500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>2490800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-826000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>3277400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-3091100</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,130 +10426,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>218000</v>
+      </c>
+      <c r="E96" s="3">
         <v>227000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>228000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>233000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>213000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>225000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>224000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>225000</v>
       </c>
       <c r="K96" s="3">
         <v>225000</v>
       </c>
       <c r="L96" s="3">
+        <v>225000</v>
+      </c>
+      <c r="M96" s="3">
         <v>221000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>216000</v>
       </c>
       <c r="N96" s="3">
         <v>216000</v>
       </c>
       <c r="O96" s="3">
+        <v>216000</v>
+      </c>
+      <c r="P96" s="3">
         <v>215000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>221000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-205100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-209100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-369800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-156700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-154700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-141800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-141700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-142000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-141900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-141500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-284700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-143200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-145200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-132900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-134400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-139600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-139000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-143800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-227600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-112300</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-112200</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-114500</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-114100</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-116600</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-108800</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-109900</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,130 +10924,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3648000</v>
+      </c>
+      <c r="E100" s="3">
         <v>891000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1255000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1180000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>28000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1697000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4276000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1852000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6896000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6438000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1521000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>408000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3676000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1617000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1976000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6788800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-16171000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-5417500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2614400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>778700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-335900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>7644300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3442900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-826800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>18731700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4108700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-6240100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3219600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>789600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1022700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2690400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1949600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1236000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-363900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1879000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-934300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2769800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-493400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-3400400</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>2716800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1090000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2421000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2054000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-178000</v>
       </c>
-      <c r="G102" s="3">
-        <v>19000</v>
-      </c>
       <c r="H102" s="3">
+        <v>-1340000</v>
+      </c>
+      <c r="I102" s="3">
         <v>1983000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9503000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>438000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>83000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-36000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-38000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-79000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>30000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>298000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-735600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>567500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>350700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>73900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-142100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>69200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>150500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-292800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>63500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>134400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-81500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-138100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-382800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>547500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-338200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>293800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-57500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-51800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-128200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>52600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>22800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>58500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-33600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-11700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>47800</v>
       </c>
     </row>
